--- a/data/H131_20260617_20.xlsx
+++ b/data/H131_20260617_20.xlsx
@@ -450,7 +450,7 @@
         <v>667.0</v>
       </c>
       <c r="J5" t="n">
-        <v>438.0</v>
+        <v>442.0</v>
       </c>
       <c r="K5" t="n">
         <v>1.0</v>
@@ -462,10 +462,10 @@
         <v>0.0</v>
       </c>
       <c r="N5" t="n">
-        <v>438.0</v>
+        <v>442.0</v>
       </c>
       <c r="O5" t="n">
-        <v>193.0</v>
+        <v>197.0</v>
       </c>
       <c r="P5" t="n">
         <v>244.0</v>
@@ -521,7 +521,7 @@
         <v>929.0</v>
       </c>
       <c r="J6" t="n">
-        <v>636.0</v>
+        <v>637.0</v>
       </c>
       <c r="K6" t="n">
         <v>1.0</v>
@@ -533,10 +533,10 @@
         <v>0.0</v>
       </c>
       <c r="N6" t="n">
-        <v>636.0</v>
+        <v>637.0</v>
       </c>
       <c r="O6" t="n">
-        <v>290.0</v>
+        <v>291.0</v>
       </c>
       <c r="P6" t="n">
         <v>346.0</v>
@@ -663,7 +663,7 @@
         <v>711.0</v>
       </c>
       <c r="J8" t="n">
-        <v>398.0</v>
+        <v>418.0</v>
       </c>
       <c r="K8" t="n">
         <v>1.0</v>
@@ -675,13 +675,13 @@
         <v>0.0</v>
       </c>
       <c r="N8" t="n">
-        <v>398.0</v>
+        <v>418.0</v>
       </c>
       <c r="O8" t="n">
-        <v>210.0</v>
+        <v>222.0</v>
       </c>
       <c r="P8" t="n">
-        <v>188.0</v>
+        <v>196.0</v>
       </c>
       <c r="Q8" t="n">
         <v>0.0</v>
@@ -947,7 +947,7 @@
         <v>815.0</v>
       </c>
       <c r="J12" t="n">
-        <v>632.0</v>
+        <v>679.0</v>
       </c>
       <c r="K12" t="n">
         <v>1.0</v>
@@ -959,13 +959,13 @@
         <v>0.0</v>
       </c>
       <c r="N12" t="n">
-        <v>632.0</v>
+        <v>679.0</v>
       </c>
       <c r="O12" t="n">
-        <v>331.0</v>
+        <v>375.0</v>
       </c>
       <c r="P12" t="n">
-        <v>301.0</v>
+        <v>304.0</v>
       </c>
       <c r="Q12" t="n">
         <v>0.0</v>
@@ -1018,7 +1018,7 @@
         <v>1245.0</v>
       </c>
       <c r="J13" t="n">
-        <v>909.0</v>
+        <v>926.0</v>
       </c>
       <c r="K13" t="n">
         <v>1.0</v>
@@ -1030,13 +1030,13 @@
         <v>0.0</v>
       </c>
       <c r="N13" t="n">
-        <v>909.0</v>
+        <v>926.0</v>
       </c>
       <c r="O13" t="n">
-        <v>451.0</v>
+        <v>461.0</v>
       </c>
       <c r="P13" t="n">
-        <v>458.0</v>
+        <v>465.0</v>
       </c>
       <c r="Q13" t="n">
         <v>0.0</v>
@@ -1089,7 +1089,7 @@
         <v>1342.0</v>
       </c>
       <c r="J14" t="n">
-        <v>653.0</v>
+        <v>655.0</v>
       </c>
       <c r="K14" t="n">
         <v>1.0</v>
@@ -1101,10 +1101,10 @@
         <v>0.0</v>
       </c>
       <c r="N14" t="n">
-        <v>653.0</v>
+        <v>655.0</v>
       </c>
       <c r="O14" t="n">
-        <v>266.0</v>
+        <v>268.0</v>
       </c>
       <c r="P14" t="n">
         <v>387.0</v>
@@ -1113,13 +1113,13 @@
         <v>0.0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U14" t="n">
         <v>0.0</v>
@@ -1128,7 +1128,7 @@
         <v>0.0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="15">
@@ -1231,7 +1231,7 @@
         <v>692.0</v>
       </c>
       <c r="J16" t="n">
-        <v>501.0</v>
+        <v>507.0</v>
       </c>
       <c r="K16" t="n">
         <v>1.0</v>
@@ -1243,13 +1243,13 @@
         <v>0.0</v>
       </c>
       <c r="N16" t="n">
-        <v>501.0</v>
+        <v>507.0</v>
       </c>
       <c r="O16" t="n">
-        <v>225.0</v>
+        <v>226.0</v>
       </c>
       <c r="P16" t="n">
-        <v>276.0</v>
+        <v>281.0</v>
       </c>
       <c r="Q16" t="n">
         <v>0.0</v>
@@ -1373,7 +1373,7 @@
         <v>1182.0</v>
       </c>
       <c r="J18" t="n">
-        <v>1071.0</v>
+        <v>1087.0</v>
       </c>
       <c r="K18" t="n">
         <v>1.0</v>
@@ -1385,13 +1385,13 @@
         <v>0.0</v>
       </c>
       <c r="N18" t="n">
-        <v>1071.0</v>
+        <v>1087.0</v>
       </c>
       <c r="O18" t="n">
-        <v>547.0</v>
+        <v>560.0</v>
       </c>
       <c r="P18" t="n">
-        <v>524.0</v>
+        <v>527.0</v>
       </c>
       <c r="Q18" t="n">
         <v>0.0</v>
@@ -1444,7 +1444,7 @@
         <v>940.0</v>
       </c>
       <c r="J19" t="n">
-        <v>555.0</v>
+        <v>561.0</v>
       </c>
       <c r="K19" t="n">
         <v>1.0</v>
@@ -1456,13 +1456,13 @@
         <v>0.0</v>
       </c>
       <c r="N19" t="n">
-        <v>555.0</v>
+        <v>561.0</v>
       </c>
       <c r="O19" t="n">
-        <v>292.0</v>
+        <v>295.0</v>
       </c>
       <c r="P19" t="n">
-        <v>263.0</v>
+        <v>266.0</v>
       </c>
       <c r="Q19" t="n">
         <v>0.0</v>
@@ -1515,7 +1515,7 @@
         <v>1257.0</v>
       </c>
       <c r="J20" t="n">
-        <v>803.0</v>
+        <v>807.0</v>
       </c>
       <c r="K20" t="n">
         <v>1.0</v>
@@ -1527,13 +1527,13 @@
         <v>1.0</v>
       </c>
       <c r="N20" t="n">
-        <v>802.0</v>
+        <v>806.0</v>
       </c>
       <c r="O20" t="n">
-        <v>438.0</v>
+        <v>440.0</v>
       </c>
       <c r="P20" t="n">
-        <v>365.0</v>
+        <v>367.0</v>
       </c>
       <c r="Q20" t="n">
         <v>0.0</v>
@@ -1586,7 +1586,7 @@
         <v>926.0</v>
       </c>
       <c r="J21" t="n">
-        <v>609.0</v>
+        <v>610.0</v>
       </c>
       <c r="K21" t="n">
         <v>1.0</v>
@@ -1598,10 +1598,10 @@
         <v>0.0</v>
       </c>
       <c r="N21" t="n">
-        <v>609.0</v>
+        <v>610.0</v>
       </c>
       <c r="O21" t="n">
-        <v>308.0</v>
+        <v>309.0</v>
       </c>
       <c r="P21" t="n">
         <v>301.0</v>
@@ -1657,7 +1657,7 @@
         <v>1003.0</v>
       </c>
       <c r="J22" t="n">
-        <v>763.0</v>
+        <v>784.0</v>
       </c>
       <c r="K22" t="n">
         <v>1.0</v>
@@ -1669,19 +1669,19 @@
         <v>0.0</v>
       </c>
       <c r="N22" t="n">
-        <v>763.0</v>
+        <v>784.0</v>
       </c>
       <c r="O22" t="n">
-        <v>435.0</v>
+        <v>439.0</v>
       </c>
       <c r="P22" t="n">
-        <v>328.0</v>
+        <v>345.0</v>
       </c>
       <c r="Q22" t="n">
         <v>0.0</v>
       </c>
       <c r="R22" t="n">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
       <c r="S22" t="n">
         <v>0.0</v>
@@ -1696,7 +1696,7 @@
         <v>0.0</v>
       </c>
       <c r="W22" t="n">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="23">
@@ -1870,7 +1870,7 @@
         <v>372.0</v>
       </c>
       <c r="J25" t="n">
-        <v>268.0</v>
+        <v>269.0</v>
       </c>
       <c r="K25" t="n">
         <v>1.0</v>
@@ -1882,10 +1882,10 @@
         <v>0.0</v>
       </c>
       <c r="N25" t="n">
-        <v>268.0</v>
+        <v>269.0</v>
       </c>
       <c r="O25" t="n">
-        <v>181.0</v>
+        <v>182.0</v>
       </c>
       <c r="P25" t="n">
         <v>87.0</v>
@@ -2083,7 +2083,7 @@
         <v>1349.0</v>
       </c>
       <c r="J28" t="n">
-        <v>931.0</v>
+        <v>933.0</v>
       </c>
       <c r="K28" t="n">
         <v>1.0</v>
@@ -2095,13 +2095,13 @@
         <v>0.0</v>
       </c>
       <c r="N28" t="n">
-        <v>931.0</v>
+        <v>933.0</v>
       </c>
       <c r="O28" t="n">
-        <v>492.0</v>
+        <v>493.0</v>
       </c>
       <c r="P28" t="n">
-        <v>437.0</v>
+        <v>438.0</v>
       </c>
       <c r="Q28" t="n">
         <v>2.0</v>
@@ -2296,7 +2296,7 @@
         <v>1214.0</v>
       </c>
       <c r="J31" t="n">
-        <v>546.0</v>
+        <v>555.0</v>
       </c>
       <c r="K31" t="n">
         <v>1.0</v>
@@ -2308,13 +2308,13 @@
         <v>0.0</v>
       </c>
       <c r="N31" t="n">
-        <v>546.0</v>
+        <v>555.0</v>
       </c>
       <c r="O31" t="n">
-        <v>261.0</v>
+        <v>269.0</v>
       </c>
       <c r="P31" t="n">
-        <v>280.0</v>
+        <v>281.0</v>
       </c>
       <c r="Q31" t="n">
         <v>5.0</v>
@@ -2367,7 +2367,7 @@
         <v>1143.0</v>
       </c>
       <c r="J32" t="n">
-        <v>655.0</v>
+        <v>658.0</v>
       </c>
       <c r="K32" t="n">
         <v>1.0</v>
@@ -2379,13 +2379,13 @@
         <v>0.0</v>
       </c>
       <c r="N32" t="n">
-        <v>655.0</v>
+        <v>658.0</v>
       </c>
       <c r="O32" t="n">
-        <v>310.0</v>
+        <v>312.0</v>
       </c>
       <c r="P32" t="n">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="Q32" t="n">
         <v>17.0</v>
@@ -2438,7 +2438,7 @@
         <v>346.0</v>
       </c>
       <c r="J33" t="n">
-        <v>286.0</v>
+        <v>287.0</v>
       </c>
       <c r="K33" t="n">
         <v>1.0</v>
@@ -2450,10 +2450,10 @@
         <v>0.0</v>
       </c>
       <c r="N33" t="n">
-        <v>286.0</v>
+        <v>287.0</v>
       </c>
       <c r="O33" t="n">
-        <v>119.0</v>
+        <v>120.0</v>
       </c>
       <c r="P33" t="n">
         <v>167.0</v>
@@ -2675,22 +2675,22 @@
         <v>0.0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="T36" t="n">
         <v>0.0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="V36" t="n">
         <v>0.0</v>
       </c>
       <c r="W36" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="37">
@@ -2722,7 +2722,7 @@
         <v>586.0</v>
       </c>
       <c r="J37" t="n">
-        <v>416.0</v>
+        <v>422.0</v>
       </c>
       <c r="K37" t="n">
         <v>1.0</v>
@@ -2734,13 +2734,13 @@
         <v>0.0</v>
       </c>
       <c r="N37" t="n">
-        <v>416.0</v>
+        <v>422.0</v>
       </c>
       <c r="O37" t="n">
-        <v>217.0</v>
+        <v>219.0</v>
       </c>
       <c r="P37" t="n">
-        <v>195.0</v>
+        <v>199.0</v>
       </c>
       <c r="Q37" t="n">
         <v>4.0</v>
@@ -2793,7 +2793,7 @@
         <v>1123.0</v>
       </c>
       <c r="J38" t="n">
-        <v>886.0</v>
+        <v>888.0</v>
       </c>
       <c r="K38" t="n">
         <v>1.0</v>
@@ -2805,10 +2805,10 @@
         <v>0.0</v>
       </c>
       <c r="N38" t="n">
-        <v>886.0</v>
+        <v>888.0</v>
       </c>
       <c r="O38" t="n">
-        <v>513.0</v>
+        <v>515.0</v>
       </c>
       <c r="P38" t="n">
         <v>373.0</v>
@@ -3006,7 +3006,7 @@
         <v>1244.0</v>
       </c>
       <c r="J41" t="n">
-        <v>783.0</v>
+        <v>809.0</v>
       </c>
       <c r="K41" t="n">
         <v>1.0</v>
@@ -3018,13 +3018,13 @@
         <v>0.0</v>
       </c>
       <c r="N41" t="n">
-        <v>783.0</v>
+        <v>809.0</v>
       </c>
       <c r="O41" t="n">
-        <v>344.0</v>
+        <v>369.0</v>
       </c>
       <c r="P41" t="n">
-        <v>439.0</v>
+        <v>440.0</v>
       </c>
       <c r="Q41" t="n">
         <v>0.0</v>
@@ -3077,7 +3077,7 @@
         <v>1005.0</v>
       </c>
       <c r="J42" t="n">
-        <v>394.0</v>
+        <v>404.0</v>
       </c>
       <c r="K42" t="n">
         <v>1.0</v>
@@ -3089,13 +3089,13 @@
         <v>0.0</v>
       </c>
       <c r="N42" t="n">
-        <v>394.0</v>
+        <v>404.0</v>
       </c>
       <c r="O42" t="n">
-        <v>248.0</v>
+        <v>254.0</v>
       </c>
       <c r="P42" t="n">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="Q42" t="n">
         <v>0.0</v>
@@ -3290,7 +3290,7 @@
         <v>1213.0</v>
       </c>
       <c r="J45" t="n">
-        <v>947.0</v>
+        <v>962.0</v>
       </c>
       <c r="K45" t="n">
         <v>1.0</v>
@@ -3302,16 +3302,16 @@
         <v>1.0</v>
       </c>
       <c r="N45" t="n">
-        <v>946.0</v>
+        <v>961.0</v>
       </c>
       <c r="O45" t="n">
-        <v>437.0</v>
+        <v>445.0</v>
       </c>
       <c r="P45" t="n">
-        <v>508.0</v>
+        <v>512.0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="R45" t="n">
         <v>48.0</v>
@@ -3361,7 +3361,7 @@
         <v>1429.0</v>
       </c>
       <c r="J46" t="n">
-        <v>1304.0</v>
+        <v>1347.0</v>
       </c>
       <c r="K46" t="n">
         <v>1.0</v>
@@ -3373,25 +3373,25 @@
         <v>0.0</v>
       </c>
       <c r="N46" t="n">
-        <v>1304.0</v>
+        <v>1347.0</v>
       </c>
       <c r="O46" t="n">
-        <v>674.0</v>
+        <v>699.0</v>
       </c>
       <c r="P46" t="n">
-        <v>602.0</v>
+        <v>603.0</v>
       </c>
       <c r="Q46" t="n">
-        <v>28.0</v>
+        <v>45.0</v>
       </c>
       <c r="R46" t="n">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="S46" t="n">
         <v>12.0</v>
       </c>
       <c r="T46" t="n">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U46" t="n">
         <v>0.0</v>
@@ -3400,7 +3400,7 @@
         <v>0.0</v>
       </c>
       <c r="W46" t="n">
-        <v>38.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="47">
@@ -3503,7 +3503,7 @@
         <v>1102.0</v>
       </c>
       <c r="J48" t="n">
-        <v>815.0</v>
+        <v>840.0</v>
       </c>
       <c r="K48" t="n">
         <v>1.0</v>
@@ -3515,10 +3515,10 @@
         <v>0.0</v>
       </c>
       <c r="N48" t="n">
-        <v>815.0</v>
+        <v>840.0</v>
       </c>
       <c r="O48" t="n">
-        <v>441.0</v>
+        <v>466.0</v>
       </c>
       <c r="P48" t="n">
         <v>374.0</v>
@@ -3716,7 +3716,7 @@
         <v>878.0</v>
       </c>
       <c r="J51" t="n">
-        <v>658.0</v>
+        <v>661.0</v>
       </c>
       <c r="K51" t="n">
         <v>1.0</v>
@@ -3728,13 +3728,13 @@
         <v>0.0</v>
       </c>
       <c r="N51" t="n">
-        <v>658.0</v>
+        <v>661.0</v>
       </c>
       <c r="O51" t="n">
         <v>277.0</v>
       </c>
       <c r="P51" t="n">
-        <v>381.0</v>
+        <v>384.0</v>
       </c>
       <c r="Q51" t="n">
         <v>0.0</v>
@@ -3787,7 +3787,7 @@
         <v>605.0</v>
       </c>
       <c r="J52" t="n">
-        <v>474.0</v>
+        <v>480.0</v>
       </c>
       <c r="K52" t="n">
         <v>1.0</v>
@@ -3799,19 +3799,19 @@
         <v>0.0</v>
       </c>
       <c r="N52" t="n">
-        <v>474.0</v>
+        <v>480.0</v>
       </c>
       <c r="O52" t="n">
-        <v>221.0</v>
+        <v>222.0</v>
       </c>
       <c r="P52" t="n">
-        <v>253.0</v>
+        <v>258.0</v>
       </c>
       <c r="Q52" t="n">
         <v>0.0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="S52" t="n">
         <v>3.0</v>
@@ -3826,7 +3826,7 @@
         <v>0.0</v>
       </c>
       <c r="W52" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="53">
@@ -4071,7 +4071,7 @@
         <v>615.0</v>
       </c>
       <c r="J56" t="n">
-        <v>495.0</v>
+        <v>507.0</v>
       </c>
       <c r="K56" t="n">
         <v>1.0</v>
@@ -4083,13 +4083,13 @@
         <v>0.0</v>
       </c>
       <c r="N56" t="n">
-        <v>495.0</v>
+        <v>507.0</v>
       </c>
       <c r="O56" t="n">
-        <v>218.0</v>
+        <v>226.0</v>
       </c>
       <c r="P56" t="n">
-        <v>277.0</v>
+        <v>281.0</v>
       </c>
       <c r="Q56" t="n">
         <v>0.0</v>
@@ -4142,7 +4142,7 @@
         <v>620.0</v>
       </c>
       <c r="J57" t="n">
-        <v>435.0</v>
+        <v>445.0</v>
       </c>
       <c r="K57" t="n">
         <v>1.0</v>
@@ -4154,10 +4154,10 @@
         <v>0.0</v>
       </c>
       <c r="N57" t="n">
-        <v>435.0</v>
+        <v>445.0</v>
       </c>
       <c r="O57" t="n">
-        <v>435.0</v>
+        <v>445.0</v>
       </c>
       <c r="P57" t="n">
         <v>0.0</v>
@@ -4213,7 +4213,7 @@
         <v>1059.0</v>
       </c>
       <c r="J58" t="n">
-        <v>631.0</v>
+        <v>646.0</v>
       </c>
       <c r="K58" t="n">
         <v>1.0</v>
@@ -4225,13 +4225,13 @@
         <v>0.0</v>
       </c>
       <c r="N58" t="n">
-        <v>631.0</v>
+        <v>646.0</v>
       </c>
       <c r="O58" t="n">
-        <v>292.0</v>
+        <v>299.0</v>
       </c>
       <c r="P58" t="n">
-        <v>339.0</v>
+        <v>347.0</v>
       </c>
       <c r="Q58" t="n">
         <v>0.0</v>
@@ -4355,7 +4355,7 @@
         <v>707.0</v>
       </c>
       <c r="J60" t="n">
-        <v>574.0</v>
+        <v>587.0</v>
       </c>
       <c r="K60" t="n">
         <v>1.0</v>
@@ -4367,10 +4367,10 @@
         <v>0.0</v>
       </c>
       <c r="N60" t="n">
-        <v>574.0</v>
+        <v>587.0</v>
       </c>
       <c r="O60" t="n">
-        <v>243.0</v>
+        <v>256.0</v>
       </c>
       <c r="P60" t="n">
         <v>331.0</v>
@@ -4423,10 +4423,10 @@
         <v>1087.0</v>
       </c>
       <c r="I61" t="n">
-        <v>1074.0</v>
+        <v>1075.0</v>
       </c>
       <c r="J61" t="n">
-        <v>759.0</v>
+        <v>772.0</v>
       </c>
       <c r="K61" t="n">
         <v>1.0</v>
@@ -4438,13 +4438,13 @@
         <v>0.0</v>
       </c>
       <c r="N61" t="n">
-        <v>759.0</v>
+        <v>772.0</v>
       </c>
       <c r="O61" t="n">
-        <v>366.0</v>
+        <v>378.0</v>
       </c>
       <c r="P61" t="n">
-        <v>393.0</v>
+        <v>394.0</v>
       </c>
       <c r="Q61" t="n">
         <v>0.0</v>
@@ -4497,7 +4497,7 @@
         <v>570.0</v>
       </c>
       <c r="J62" t="n">
-        <v>491.0</v>
+        <v>493.0</v>
       </c>
       <c r="K62" t="n">
         <v>1.0</v>
@@ -4509,10 +4509,10 @@
         <v>0.0</v>
       </c>
       <c r="N62" t="n">
-        <v>491.0</v>
+        <v>493.0</v>
       </c>
       <c r="O62" t="n">
-        <v>263.0</v>
+        <v>265.0</v>
       </c>
       <c r="P62" t="n">
         <v>228.0</v>
@@ -4568,7 +4568,7 @@
         <v>1161.0</v>
       </c>
       <c r="J63" t="n">
-        <v>641.0</v>
+        <v>643.0</v>
       </c>
       <c r="K63" t="n">
         <v>1.0</v>
@@ -4580,10 +4580,10 @@
         <v>0.0</v>
       </c>
       <c r="N63" t="n">
-        <v>641.0</v>
+        <v>643.0</v>
       </c>
       <c r="O63" t="n">
-        <v>302.0</v>
+        <v>304.0</v>
       </c>
       <c r="P63" t="n">
         <v>339.0</v>
@@ -4639,7 +4639,7 @@
         <v>1113.0</v>
       </c>
       <c r="J64" t="n">
-        <v>1019.0</v>
+        <v>1029.0</v>
       </c>
       <c r="K64" t="n">
         <v>1.0</v>
@@ -4651,13 +4651,13 @@
         <v>0.0</v>
       </c>
       <c r="N64" t="n">
-        <v>1019.0</v>
+        <v>1029.0</v>
       </c>
       <c r="O64" t="n">
-        <v>567.0</v>
+        <v>576.0</v>
       </c>
       <c r="P64" t="n">
-        <v>452.0</v>
+        <v>453.0</v>
       </c>
       <c r="Q64" t="n">
         <v>0.0</v>
@@ -4710,7 +4710,7 @@
         <v>522.0</v>
       </c>
       <c r="J65" t="n">
-        <v>445.0</v>
+        <v>456.0</v>
       </c>
       <c r="K65" t="n">
         <v>1.0</v>
@@ -4722,13 +4722,13 @@
         <v>0.0</v>
       </c>
       <c r="N65" t="n">
-        <v>445.0</v>
+        <v>456.0</v>
       </c>
       <c r="O65" t="n">
-        <v>246.0</v>
+        <v>256.0</v>
       </c>
       <c r="P65" t="n">
-        <v>199.0</v>
+        <v>200.0</v>
       </c>
       <c r="Q65" t="n">
         <v>0.0</v>
@@ -4781,7 +4781,7 @@
         <v>1155.0</v>
       </c>
       <c r="J66" t="n">
-        <v>997.0</v>
+        <v>1018.0</v>
       </c>
       <c r="K66" t="n">
         <v>1.0</v>
@@ -4793,22 +4793,22 @@
         <v>0.0</v>
       </c>
       <c r="N66" t="n">
-        <v>997.0</v>
+        <v>1018.0</v>
       </c>
       <c r="O66" t="n">
-        <v>541.0</v>
+        <v>555.0</v>
       </c>
       <c r="P66" t="n">
-        <v>456.0</v>
+        <v>462.0</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R66" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="S66" t="n">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="T66" t="n">
         <v>0.0</v>
@@ -4820,7 +4820,7 @@
         <v>0.0</v>
       </c>
       <c r="W66" t="n">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="67">
@@ -4852,7 +4852,7 @@
         <v>1129.0</v>
       </c>
       <c r="J67" t="n">
-        <v>902.0</v>
+        <v>909.0</v>
       </c>
       <c r="K67" t="n">
         <v>1.0</v>
@@ -4864,22 +4864,22 @@
         <v>0.0</v>
       </c>
       <c r="N67" t="n">
-        <v>902.0</v>
+        <v>909.0</v>
       </c>
       <c r="O67" t="n">
-        <v>407.0</v>
+        <v>410.0</v>
       </c>
       <c r="P67" t="n">
-        <v>495.0</v>
+        <v>498.0</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R67" t="n">
         <v>0.0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T67" t="n">
         <v>0.0</v>
@@ -4891,7 +4891,7 @@
         <v>0.0</v>
       </c>
       <c r="W67" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="68">
@@ -5065,7 +5065,7 @@
         <v>1151.0</v>
       </c>
       <c r="J70" t="n">
-        <v>952.0</v>
+        <v>970.0</v>
       </c>
       <c r="K70" t="n">
         <v>1.0</v>
@@ -5077,16 +5077,16 @@
         <v>0.0</v>
       </c>
       <c r="N70" t="n">
-        <v>952.0</v>
+        <v>970.0</v>
       </c>
       <c r="O70" t="n">
-        <v>586.0</v>
+        <v>599.0</v>
       </c>
       <c r="P70" t="n">
-        <v>359.0</v>
+        <v>362.0</v>
       </c>
       <c r="Q70" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="R70" t="n">
         <v>9.0</v>
@@ -5278,7 +5278,7 @@
         <v>973.0</v>
       </c>
       <c r="J73" t="n">
-        <v>855.0</v>
+        <v>861.0</v>
       </c>
       <c r="K73" t="n">
         <v>1.0</v>
@@ -5290,13 +5290,13 @@
         <v>0.0</v>
       </c>
       <c r="N73" t="n">
-        <v>855.0</v>
+        <v>861.0</v>
       </c>
       <c r="O73" t="n">
-        <v>409.0</v>
+        <v>414.0</v>
       </c>
       <c r="P73" t="n">
-        <v>439.0</v>
+        <v>440.0</v>
       </c>
       <c r="Q73" t="n">
         <v>7.0</v>
@@ -5420,7 +5420,7 @@
         <v>877.0</v>
       </c>
       <c r="J75" t="n">
-        <v>780.0</v>
+        <v>782.0</v>
       </c>
       <c r="K75" t="n">
         <v>1.0</v>
@@ -5432,10 +5432,10 @@
         <v>0.0</v>
       </c>
       <c r="N75" t="n">
-        <v>780.0</v>
+        <v>782.0</v>
       </c>
       <c r="O75" t="n">
-        <v>406.0</v>
+        <v>408.0</v>
       </c>
       <c r="P75" t="n">
         <v>373.0</v>
@@ -5447,7 +5447,7 @@
         <v>4.0</v>
       </c>
       <c r="S75" t="n">
-        <v>40.0</v>
+        <v>42.0</v>
       </c>
       <c r="T75" t="n">
         <v>2.0</v>
@@ -5459,7 +5459,7 @@
         <v>0.0</v>
       </c>
       <c r="W75" t="n">
-        <v>51.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="76">
@@ -5775,7 +5775,7 @@
         <v>1333.0</v>
       </c>
       <c r="J80" t="n">
-        <v>799.0</v>
+        <v>804.0</v>
       </c>
       <c r="K80" t="n">
         <v>1.0</v>
@@ -5787,13 +5787,13 @@
         <v>0.0</v>
       </c>
       <c r="N80" t="n">
-        <v>799.0</v>
+        <v>804.0</v>
       </c>
       <c r="O80" t="n">
-        <v>436.0</v>
+        <v>440.0</v>
       </c>
       <c r="P80" t="n">
-        <v>363.0</v>
+        <v>364.0</v>
       </c>
       <c r="Q80" t="n">
         <v>0.0</v>
@@ -5846,7 +5846,7 @@
         <v>796.0</v>
       </c>
       <c r="J81" t="n">
-        <v>658.0</v>
+        <v>667.0</v>
       </c>
       <c r="K81" t="n">
         <v>1.0</v>
@@ -5858,13 +5858,13 @@
         <v>0.0</v>
       </c>
       <c r="N81" t="n">
-        <v>658.0</v>
+        <v>667.0</v>
       </c>
       <c r="O81" t="n">
-        <v>341.0</v>
+        <v>346.0</v>
       </c>
       <c r="P81" t="n">
-        <v>317.0</v>
+        <v>321.0</v>
       </c>
       <c r="Q81" t="n">
         <v>0.0</v>
@@ -5917,7 +5917,7 @@
         <v>1157.0</v>
       </c>
       <c r="J82" t="n">
-        <v>800.0</v>
+        <v>813.0</v>
       </c>
       <c r="K82" t="n">
         <v>1.0</v>
@@ -5929,10 +5929,10 @@
         <v>0.0</v>
       </c>
       <c r="N82" t="n">
-        <v>800.0</v>
+        <v>813.0</v>
       </c>
       <c r="O82" t="n">
-        <v>368.0</v>
+        <v>381.0</v>
       </c>
       <c r="P82" t="n">
         <v>432.0</v>
@@ -5988,7 +5988,7 @@
         <v>1127.0</v>
       </c>
       <c r="J83" t="n">
-        <v>680.0</v>
+        <v>681.0</v>
       </c>
       <c r="K83" t="n">
         <v>1.0</v>
@@ -6000,10 +6000,10 @@
         <v>0.0</v>
       </c>
       <c r="N83" t="n">
-        <v>680.0</v>
+        <v>681.0</v>
       </c>
       <c r="O83" t="n">
-        <v>269.0</v>
+        <v>270.0</v>
       </c>
       <c r="P83" t="n">
         <v>411.0</v>
@@ -6130,7 +6130,7 @@
         <v>1308.0</v>
       </c>
       <c r="J85" t="n">
-        <v>962.0</v>
+        <v>1000.0</v>
       </c>
       <c r="K85" t="n">
         <v>1.0</v>
@@ -6142,13 +6142,13 @@
         <v>0.0</v>
       </c>
       <c r="N85" t="n">
-        <v>962.0</v>
+        <v>1000.0</v>
       </c>
       <c r="O85" t="n">
-        <v>447.0</v>
+        <v>470.0</v>
       </c>
       <c r="P85" t="n">
-        <v>515.0</v>
+        <v>530.0</v>
       </c>
       <c r="Q85" t="n">
         <v>0.0</v>
@@ -6201,7 +6201,7 @@
         <v>1249.0</v>
       </c>
       <c r="J86" t="n">
-        <v>766.0</v>
+        <v>780.0</v>
       </c>
       <c r="K86" t="n">
         <v>1.0</v>
@@ -6213,13 +6213,13 @@
         <v>0.0</v>
       </c>
       <c r="N86" t="n">
-        <v>766.0</v>
+        <v>780.0</v>
       </c>
       <c r="O86" t="n">
-        <v>358.0</v>
+        <v>364.0</v>
       </c>
       <c r="P86" t="n">
-        <v>408.0</v>
+        <v>416.0</v>
       </c>
       <c r="Q86" t="n">
         <v>0.0</v>
@@ -6272,7 +6272,7 @@
         <v>735.0</v>
       </c>
       <c r="J87" t="n">
-        <v>629.0</v>
+        <v>640.0</v>
       </c>
       <c r="K87" t="n">
         <v>1.0</v>
@@ -6284,13 +6284,13 @@
         <v>0.0</v>
       </c>
       <c r="N87" t="n">
-        <v>629.0</v>
+        <v>640.0</v>
       </c>
       <c r="O87" t="n">
-        <v>319.0</v>
+        <v>324.0</v>
       </c>
       <c r="P87" t="n">
-        <v>310.0</v>
+        <v>316.0</v>
       </c>
       <c r="Q87" t="n">
         <v>0.0</v>
@@ -6343,7 +6343,7 @@
         <v>882.0</v>
       </c>
       <c r="J88" t="n">
-        <v>590.0</v>
+        <v>593.0</v>
       </c>
       <c r="K88" t="n">
         <v>1.0</v>
@@ -6355,10 +6355,10 @@
         <v>0.0</v>
       </c>
       <c r="N88" t="n">
-        <v>590.0</v>
+        <v>593.0</v>
       </c>
       <c r="O88" t="n">
-        <v>274.0</v>
+        <v>277.0</v>
       </c>
       <c r="P88" t="n">
         <v>316.0</v>
@@ -6485,7 +6485,7 @@
         <v>744.0</v>
       </c>
       <c r="J90" t="n">
-        <v>637.0</v>
+        <v>643.0</v>
       </c>
       <c r="K90" t="n">
         <v>1.0</v>
@@ -6497,13 +6497,13 @@
         <v>0.0</v>
       </c>
       <c r="N90" t="n">
-        <v>637.0</v>
+        <v>643.0</v>
       </c>
       <c r="O90" t="n">
-        <v>322.0</v>
+        <v>326.0</v>
       </c>
       <c r="P90" t="n">
-        <v>314.0</v>
+        <v>316.0</v>
       </c>
       <c r="Q90" t="n">
         <v>1.0</v>
@@ -6556,7 +6556,7 @@
         <v>940.0</v>
       </c>
       <c r="J91" t="n">
-        <v>532.0</v>
+        <v>579.0</v>
       </c>
       <c r="K91" t="n">
         <v>1.0</v>
@@ -6568,16 +6568,16 @@
         <v>0.0</v>
       </c>
       <c r="N91" t="n">
-        <v>532.0</v>
+        <v>579.0</v>
       </c>
       <c r="O91" t="n">
-        <v>82.0</v>
+        <v>108.0</v>
       </c>
       <c r="P91" t="n">
         <v>307.0</v>
       </c>
       <c r="Q91" t="n">
-        <v>143.0</v>
+        <v>164.0</v>
       </c>
       <c r="R91" t="n">
         <v>39.0</v>
@@ -6627,7 +6627,7 @@
         <v>1315.0</v>
       </c>
       <c r="J92" t="n">
-        <v>457.0</v>
+        <v>478.0</v>
       </c>
       <c r="K92" t="n">
         <v>1.0</v>
@@ -6639,22 +6639,22 @@
         <v>0.0</v>
       </c>
       <c r="N92" t="n">
-        <v>457.0</v>
+        <v>478.0</v>
       </c>
       <c r="O92" t="n">
-        <v>196.0</v>
+        <v>203.0</v>
       </c>
       <c r="P92" t="n">
-        <v>210.0</v>
+        <v>221.0</v>
       </c>
       <c r="Q92" t="n">
-        <v>51.0</v>
+        <v>54.0</v>
       </c>
       <c r="R92" t="n">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
       <c r="S92" t="n">
-        <v>60.0</v>
+        <v>68.0</v>
       </c>
       <c r="T92" t="n">
         <v>7.0</v>
@@ -6666,7 +6666,7 @@
         <v>2.0</v>
       </c>
       <c r="W92" t="n">
-        <v>108.0</v>
+        <v>118.0</v>
       </c>
     </row>
     <row r="93">
@@ -6769,7 +6769,7 @@
         <v>833.0</v>
       </c>
       <c r="J94" t="n">
-        <v>506.0</v>
+        <v>522.0</v>
       </c>
       <c r="K94" t="n">
         <v>1.0</v>
@@ -6781,13 +6781,13 @@
         <v>0.0</v>
       </c>
       <c r="N94" t="n">
-        <v>506.0</v>
+        <v>522.0</v>
       </c>
       <c r="O94" t="n">
-        <v>218.0</v>
+        <v>225.0</v>
       </c>
       <c r="P94" t="n">
-        <v>288.0</v>
+        <v>297.0</v>
       </c>
       <c r="Q94" t="n">
         <v>0.0</v>
@@ -6840,7 +6840,7 @@
         <v>1421.0</v>
       </c>
       <c r="J95" t="n">
-        <v>1166.0</v>
+        <v>1172.0</v>
       </c>
       <c r="K95" t="n">
         <v>1.0</v>
@@ -6852,10 +6852,10 @@
         <v>0.0</v>
       </c>
       <c r="N95" t="n">
-        <v>1166.0</v>
+        <v>1172.0</v>
       </c>
       <c r="O95" t="n">
-        <v>523.0</v>
+        <v>529.0</v>
       </c>
       <c r="P95" t="n">
         <v>643.0</v>
@@ -6911,7 +6911,7 @@
         <v>1426.0</v>
       </c>
       <c r="J96" t="n">
-        <v>604.0</v>
+        <v>616.0</v>
       </c>
       <c r="K96" t="n">
         <v>1.0</v>
@@ -6923,13 +6923,13 @@
         <v>0.0</v>
       </c>
       <c r="N96" t="n">
-        <v>604.0</v>
+        <v>616.0</v>
       </c>
       <c r="O96" t="n">
-        <v>274.0</v>
+        <v>285.0</v>
       </c>
       <c r="P96" t="n">
-        <v>330.0</v>
+        <v>331.0</v>
       </c>
       <c r="Q96" t="n">
         <v>0.0</v>
@@ -6982,7 +6982,7 @@
         <v>1012.0</v>
       </c>
       <c r="J97" t="n">
-        <v>575.0</v>
+        <v>596.0</v>
       </c>
       <c r="K97" t="n">
         <v>1.0</v>
@@ -6994,13 +6994,13 @@
         <v>0.0</v>
       </c>
       <c r="N97" t="n">
-        <v>575.0</v>
+        <v>596.0</v>
       </c>
       <c r="O97" t="n">
-        <v>282.0</v>
+        <v>291.0</v>
       </c>
       <c r="P97" t="n">
-        <v>293.0</v>
+        <v>305.0</v>
       </c>
       <c r="Q97" t="n">
         <v>0.0</v>
@@ -7053,7 +7053,7 @@
         <v>1461.0</v>
       </c>
       <c r="J98" t="n">
-        <v>306.0</v>
+        <v>308.0</v>
       </c>
       <c r="K98" t="n">
         <v>1.0</v>
@@ -7065,13 +7065,13 @@
         <v>0.0</v>
       </c>
       <c r="N98" t="n">
-        <v>306.0</v>
+        <v>308.0</v>
       </c>
       <c r="O98" t="n">
         <v>128.0</v>
       </c>
       <c r="P98" t="n">
-        <v>178.0</v>
+        <v>180.0</v>
       </c>
       <c r="Q98" t="n">
         <v>0.0</v>
@@ -7124,7 +7124,7 @@
         <v>878.0</v>
       </c>
       <c r="J99" t="n">
-        <v>646.0</v>
+        <v>657.0</v>
       </c>
       <c r="K99" t="n">
         <v>1.0</v>
@@ -7136,13 +7136,13 @@
         <v>0.0</v>
       </c>
       <c r="N99" t="n">
-        <v>646.0</v>
+        <v>657.0</v>
       </c>
       <c r="O99" t="n">
-        <v>325.0</v>
+        <v>331.0</v>
       </c>
       <c r="P99" t="n">
-        <v>321.0</v>
+        <v>326.0</v>
       </c>
       <c r="Q99" t="n">
         <v>0.0</v>
@@ -7266,7 +7266,7 @@
         <v>1059.0</v>
       </c>
       <c r="J101" t="n">
-        <v>924.0</v>
+        <v>926.0</v>
       </c>
       <c r="K101" t="n">
         <v>1.0</v>
@@ -7278,10 +7278,10 @@
         <v>0.0</v>
       </c>
       <c r="N101" t="n">
-        <v>924.0</v>
+        <v>926.0</v>
       </c>
       <c r="O101" t="n">
-        <v>480.0</v>
+        <v>482.0</v>
       </c>
       <c r="P101" t="n">
         <v>444.0</v>
@@ -7337,7 +7337,7 @@
         <v>1159.0</v>
       </c>
       <c r="J102" t="n">
-        <v>716.0</v>
+        <v>755.0</v>
       </c>
       <c r="K102" t="n">
         <v>1.0</v>
@@ -7349,22 +7349,22 @@
         <v>0.0</v>
       </c>
       <c r="N102" t="n">
-        <v>716.0</v>
+        <v>755.0</v>
       </c>
       <c r="O102" t="n">
-        <v>329.0</v>
+        <v>356.0</v>
       </c>
       <c r="P102" t="n">
-        <v>387.0</v>
+        <v>399.0</v>
       </c>
       <c r="Q102" t="n">
         <v>0.0</v>
       </c>
       <c r="R102" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="S102" t="n">
-        <v>9.0</v>
+        <v>14.0</v>
       </c>
       <c r="T102" t="n">
         <v>0.0</v>
@@ -7376,7 +7376,7 @@
         <v>0.0</v>
       </c>
       <c r="W102" t="n">
-        <v>41.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="103">
@@ -7550,7 +7550,7 @@
         <v>1066.0</v>
       </c>
       <c r="J105" t="n">
-        <v>630.0</v>
+        <v>631.0</v>
       </c>
       <c r="K105" t="n">
         <v>1.0</v>
@@ -7562,10 +7562,10 @@
         <v>0.0</v>
       </c>
       <c r="N105" t="n">
-        <v>630.0</v>
+        <v>631.0</v>
       </c>
       <c r="O105" t="n">
-        <v>283.0</v>
+        <v>284.0</v>
       </c>
       <c r="P105" t="n">
         <v>347.0</v>
@@ -7577,7 +7577,7 @@
         <v>34.0</v>
       </c>
       <c r="S105" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="T105" t="n">
         <v>0.0</v>
@@ -7589,7 +7589,7 @@
         <v>0.0</v>
       </c>
       <c r="W105" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
     </row>
     <row r="106">
@@ -7645,10 +7645,10 @@
         <v>10.0</v>
       </c>
       <c r="R106" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="S106" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="T106" t="n">
         <v>0.0</v>
@@ -7660,7 +7660,7 @@
         <v>0.0</v>
       </c>
       <c r="W106" t="n">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="107">
@@ -7905,7 +7905,7 @@
         <v>754.0</v>
       </c>
       <c r="J110" t="n">
-        <v>387.0</v>
+        <v>388.0</v>
       </c>
       <c r="K110" t="n">
         <v>1.0</v>
@@ -7917,10 +7917,10 @@
         <v>0.0</v>
       </c>
       <c r="N110" t="n">
-        <v>387.0</v>
+        <v>388.0</v>
       </c>
       <c r="O110" t="n">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="P110" t="n">
         <v>218.0</v>
@@ -7932,7 +7932,7 @@
         <v>5.0</v>
       </c>
       <c r="S110" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="T110" t="n">
         <v>0.0</v>
@@ -7944,7 +7944,7 @@
         <v>0.0</v>
       </c>
       <c r="W110" t="n">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="111">
@@ -8047,7 +8047,7 @@
         <v>709.0</v>
       </c>
       <c r="J112" t="n">
-        <v>413.0</v>
+        <v>431.0</v>
       </c>
       <c r="K112" t="n">
         <v>1.0</v>
@@ -8059,13 +8059,13 @@
         <v>0.0</v>
       </c>
       <c r="N112" t="n">
-        <v>413.0</v>
+        <v>431.0</v>
       </c>
       <c r="O112" t="n">
-        <v>200.0</v>
+        <v>210.0</v>
       </c>
       <c r="P112" t="n">
-        <v>209.0</v>
+        <v>217.0</v>
       </c>
       <c r="Q112" t="n">
         <v>4.0</v>
@@ -8331,7 +8331,7 @@
         <v>1148.0</v>
       </c>
       <c r="J116" t="n">
-        <v>422.0</v>
+        <v>457.0</v>
       </c>
       <c r="K116" t="n">
         <v>1.0</v>
@@ -8343,16 +8343,16 @@
         <v>1.0</v>
       </c>
       <c r="N116" t="n">
-        <v>421.0</v>
+        <v>456.0</v>
       </c>
       <c r="O116" t="n">
         <v>63.0</v>
       </c>
       <c r="P116" t="n">
-        <v>195.0</v>
+        <v>209.0</v>
       </c>
       <c r="Q116" t="n">
-        <v>164.0</v>
+        <v>185.0</v>
       </c>
       <c r="R116" t="n">
         <v>0.0</v>
@@ -8402,7 +8402,7 @@
         <v>1078.0</v>
       </c>
       <c r="J117" t="n">
-        <v>416.0</v>
+        <v>433.0</v>
       </c>
       <c r="K117" t="n">
         <v>1.0</v>
@@ -8414,13 +8414,13 @@
         <v>1.0</v>
       </c>
       <c r="N117" t="n">
-        <v>415.0</v>
+        <v>432.0</v>
       </c>
       <c r="O117" t="n">
-        <v>186.0</v>
+        <v>195.0</v>
       </c>
       <c r="P117" t="n">
-        <v>230.0</v>
+        <v>238.0</v>
       </c>
       <c r="Q117" t="n">
         <v>0.0</v>
@@ -8473,7 +8473,7 @@
         <v>1422.0</v>
       </c>
       <c r="J118" t="n">
-        <v>488.0</v>
+        <v>500.0</v>
       </c>
       <c r="K118" t="n">
         <v>1.0</v>
@@ -8485,13 +8485,13 @@
         <v>0.0</v>
       </c>
       <c r="N118" t="n">
-        <v>488.0</v>
+        <v>500.0</v>
       </c>
       <c r="O118" t="n">
-        <v>252.0</v>
+        <v>256.0</v>
       </c>
       <c r="P118" t="n">
-        <v>234.0</v>
+        <v>242.0</v>
       </c>
       <c r="Q118" t="n">
         <v>2.0</v>
@@ -8506,13 +8506,13 @@
         <v>1.0</v>
       </c>
       <c r="U118" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="V118" t="n">
         <v>2.0</v>
       </c>
       <c r="W118" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="119">
@@ -8544,7 +8544,7 @@
         <v>1084.0</v>
       </c>
       <c r="J119" t="n">
-        <v>466.0</v>
+        <v>486.0</v>
       </c>
       <c r="K119" t="n">
         <v>1.0</v>
@@ -8556,13 +8556,13 @@
         <v>0.0</v>
       </c>
       <c r="N119" t="n">
-        <v>466.0</v>
+        <v>486.0</v>
       </c>
       <c r="O119" t="n">
-        <v>256.0</v>
+        <v>272.0</v>
       </c>
       <c r="P119" t="n">
-        <v>207.0</v>
+        <v>211.0</v>
       </c>
       <c r="Q119" t="n">
         <v>3.0</v>
@@ -8615,7 +8615,7 @@
         <v>971.0</v>
       </c>
       <c r="J120" t="n">
-        <v>390.0</v>
+        <v>395.0</v>
       </c>
       <c r="K120" t="n">
         <v>1.0</v>
@@ -8627,13 +8627,13 @@
         <v>0.0</v>
       </c>
       <c r="N120" t="n">
-        <v>390.0</v>
+        <v>395.0</v>
       </c>
       <c r="O120" t="n">
-        <v>183.0</v>
+        <v>187.0</v>
       </c>
       <c r="P120" t="n">
-        <v>207.0</v>
+        <v>208.0</v>
       </c>
       <c r="Q120" t="n">
         <v>0.0</v>
@@ -8970,7 +8970,7 @@
         <v>1432.0</v>
       </c>
       <c r="J125" t="n">
-        <v>1005.0</v>
+        <v>1013.0</v>
       </c>
       <c r="K125" t="n">
         <v>1.0</v>
@@ -8982,16 +8982,16 @@
         <v>0.0</v>
       </c>
       <c r="N125" t="n">
-        <v>1005.0</v>
+        <v>1013.0</v>
       </c>
       <c r="O125" t="n">
-        <v>473.0</v>
+        <v>477.0</v>
       </c>
       <c r="P125" t="n">
-        <v>505.0</v>
+        <v>506.0</v>
       </c>
       <c r="Q125" t="n">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
       <c r="R125" t="n">
         <v>0.0</v>
@@ -9041,7 +9041,7 @@
         <v>1151.0</v>
       </c>
       <c r="J126" t="n">
-        <v>720.0</v>
+        <v>721.0</v>
       </c>
       <c r="K126" t="n">
         <v>1.0</v>
@@ -9053,10 +9053,10 @@
         <v>2.0</v>
       </c>
       <c r="N126" t="n">
-        <v>718.0</v>
+        <v>719.0</v>
       </c>
       <c r="O126" t="n">
-        <v>372.0</v>
+        <v>373.0</v>
       </c>
       <c r="P126" t="n">
         <v>348.0</v>
@@ -9183,7 +9183,7 @@
         <v>1267.0</v>
       </c>
       <c r="J128" t="n">
-        <v>752.0</v>
+        <v>768.0</v>
       </c>
       <c r="K128" t="n">
         <v>1.0</v>
@@ -9195,16 +9195,16 @@
         <v>0.0</v>
       </c>
       <c r="N128" t="n">
-        <v>752.0</v>
+        <v>768.0</v>
       </c>
       <c r="O128" t="n">
-        <v>386.0</v>
+        <v>399.0</v>
       </c>
       <c r="P128" t="n">
-        <v>365.0</v>
+        <v>367.0</v>
       </c>
       <c r="Q128" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R128" t="n">
         <v>14.0</v>
@@ -9254,7 +9254,7 @@
         <v>1387.0</v>
       </c>
       <c r="J129" t="n">
-        <v>273.0</v>
+        <v>351.0</v>
       </c>
       <c r="K129" t="n">
         <v>1.0</v>
@@ -9266,13 +9266,13 @@
         <v>0.0</v>
       </c>
       <c r="N129" t="n">
-        <v>273.0</v>
+        <v>351.0</v>
       </c>
       <c r="O129" t="n">
-        <v>99.0</v>
+        <v>170.0</v>
       </c>
       <c r="P129" t="n">
-        <v>173.0</v>
+        <v>180.0</v>
       </c>
       <c r="Q129" t="n">
         <v>1.0</v>
@@ -9325,7 +9325,7 @@
         <v>808.0</v>
       </c>
       <c r="J130" t="n">
-        <v>457.0</v>
+        <v>462.0</v>
       </c>
       <c r="K130" t="n">
         <v>1.0</v>
@@ -9337,13 +9337,13 @@
         <v>2.0</v>
       </c>
       <c r="N130" t="n">
-        <v>455.0</v>
+        <v>460.0</v>
       </c>
       <c r="O130" t="n">
-        <v>294.0</v>
+        <v>297.0</v>
       </c>
       <c r="P130" t="n">
-        <v>145.0</v>
+        <v>147.0</v>
       </c>
       <c r="Q130" t="n">
         <v>18.0</v>
@@ -9467,7 +9467,7 @@
         <v>1427.0</v>
       </c>
       <c r="J132" t="n">
-        <v>401.0</v>
+        <v>474.0</v>
       </c>
       <c r="K132" t="n">
         <v>1.0</v>
@@ -9479,19 +9479,19 @@
         <v>4.0</v>
       </c>
       <c r="N132" t="n">
-        <v>397.0</v>
+        <v>470.0</v>
       </c>
       <c r="O132" t="n">
-        <v>160.0</v>
+        <v>199.0</v>
       </c>
       <c r="P132" t="n">
-        <v>234.0</v>
+        <v>268.0</v>
       </c>
       <c r="Q132" t="n">
         <v>7.0</v>
       </c>
       <c r="R132" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S132" t="n">
         <v>0.0</v>
@@ -9506,7 +9506,7 @@
         <v>0.0</v>
       </c>
       <c r="W132" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="133">
@@ -9538,7 +9538,7 @@
         <v>1330.0</v>
       </c>
       <c r="J133" t="n">
-        <v>550.0</v>
+        <v>650.0</v>
       </c>
       <c r="K133" t="n">
         <v>1.0</v>
@@ -9550,13 +9550,13 @@
         <v>0.0</v>
       </c>
       <c r="N133" t="n">
-        <v>550.0</v>
+        <v>650.0</v>
       </c>
       <c r="O133" t="n">
-        <v>278.0</v>
+        <v>337.0</v>
       </c>
       <c r="P133" t="n">
-        <v>261.0</v>
+        <v>302.0</v>
       </c>
       <c r="Q133" t="n">
         <v>11.0</v>
@@ -9609,7 +9609,7 @@
         <v>1343.0</v>
       </c>
       <c r="J134" t="n">
-        <v>1070.0</v>
+        <v>1082.0</v>
       </c>
       <c r="K134" t="n">
         <v>1.0</v>
@@ -9621,13 +9621,13 @@
         <v>1.0</v>
       </c>
       <c r="N134" t="n">
-        <v>1069.0</v>
+        <v>1081.0</v>
       </c>
       <c r="O134" t="n">
-        <v>689.0</v>
+        <v>697.0</v>
       </c>
       <c r="P134" t="n">
-        <v>379.0</v>
+        <v>383.0</v>
       </c>
       <c r="Q134" t="n">
         <v>2.0</v>
@@ -9680,7 +9680,7 @@
         <v>1247.0</v>
       </c>
       <c r="J135" t="n">
-        <v>668.0</v>
+        <v>681.0</v>
       </c>
       <c r="K135" t="n">
         <v>1.0</v>
@@ -9692,13 +9692,13 @@
         <v>1.0</v>
       </c>
       <c r="N135" t="n">
-        <v>667.0</v>
+        <v>680.0</v>
       </c>
       <c r="O135" t="n">
-        <v>327.0</v>
+        <v>334.0</v>
       </c>
       <c r="P135" t="n">
-        <v>259.0</v>
+        <v>265.0</v>
       </c>
       <c r="Q135" t="n">
         <v>82.0</v>
@@ -9751,7 +9751,7 @@
         <v>1122.0</v>
       </c>
       <c r="J136" t="n">
-        <v>534.0</v>
+        <v>542.0</v>
       </c>
       <c r="K136" t="n">
         <v>1.0</v>
@@ -9763,16 +9763,16 @@
         <v>0.0</v>
       </c>
       <c r="N136" t="n">
-        <v>534.0</v>
+        <v>542.0</v>
       </c>
       <c r="O136" t="n">
-        <v>284.0</v>
+        <v>290.0</v>
       </c>
       <c r="P136" t="n">
-        <v>242.0</v>
+        <v>243.0</v>
       </c>
       <c r="Q136" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="R136" t="n">
         <v>16.0</v>
@@ -9822,7 +9822,7 @@
         <v>1211.0</v>
       </c>
       <c r="J137" t="n">
-        <v>338.0</v>
+        <v>380.0</v>
       </c>
       <c r="K137" t="n">
         <v>1.0</v>
@@ -9834,22 +9834,22 @@
         <v>0.0</v>
       </c>
       <c r="N137" t="n">
-        <v>338.0</v>
+        <v>380.0</v>
       </c>
       <c r="O137" t="n">
-        <v>110.0</v>
+        <v>137.0</v>
       </c>
       <c r="P137" t="n">
-        <v>215.0</v>
+        <v>230.0</v>
       </c>
       <c r="Q137" t="n">
         <v>13.0</v>
       </c>
       <c r="R137" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="S137" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T137" t="n">
         <v>0.0</v>
@@ -9861,7 +9861,7 @@
         <v>0.0</v>
       </c>
       <c r="W137" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="138">
@@ -9964,7 +9964,7 @@
         <v>1300.0</v>
       </c>
       <c r="J139" t="n">
-        <v>660.0</v>
+        <v>690.0</v>
       </c>
       <c r="K139" t="n">
         <v>1.0</v>
@@ -9976,13 +9976,13 @@
         <v>1.0</v>
       </c>
       <c r="N139" t="n">
-        <v>659.0</v>
+        <v>689.0</v>
       </c>
       <c r="O139" t="n">
-        <v>384.0</v>
+        <v>409.0</v>
       </c>
       <c r="P139" t="n">
-        <v>255.0</v>
+        <v>260.0</v>
       </c>
       <c r="Q139" t="n">
         <v>21.0</v>
@@ -10106,22 +10106,22 @@
         <v>1244.0</v>
       </c>
       <c r="J141" t="n">
+        <v>507.0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N141" t="n">
         <v>506.0</v>
       </c>
-      <c r="K141" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L141" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M141" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N141" t="n">
-        <v>505.0</v>
-      </c>
       <c r="O141" t="n">
-        <v>277.0</v>
+        <v>278.0</v>
       </c>
       <c r="P141" t="n">
         <v>229.0</v>
@@ -10177,7 +10177,7 @@
         <v>1047.0</v>
       </c>
       <c r="J142" t="n">
-        <v>764.0</v>
+        <v>779.0</v>
       </c>
       <c r="K142" t="n">
         <v>1.0</v>
@@ -10189,13 +10189,13 @@
         <v>0.0</v>
       </c>
       <c r="N142" t="n">
-        <v>764.0</v>
+        <v>779.0</v>
       </c>
       <c r="O142" t="n">
-        <v>408.0</v>
+        <v>416.0</v>
       </c>
       <c r="P142" t="n">
-        <v>356.0</v>
+        <v>363.0</v>
       </c>
       <c r="Q142" t="n">
         <v>0.0</v>
@@ -10319,7 +10319,7 @@
         <v>1487.0</v>
       </c>
       <c r="J144" t="n">
-        <v>694.0</v>
+        <v>705.0</v>
       </c>
       <c r="K144" t="n">
         <v>1.0</v>
@@ -10331,13 +10331,13 @@
         <v>0.0</v>
       </c>
       <c r="N144" t="n">
-        <v>694.0</v>
+        <v>705.0</v>
       </c>
       <c r="O144" t="n">
-        <v>355.0</v>
+        <v>362.0</v>
       </c>
       <c r="P144" t="n">
-        <v>339.0</v>
+        <v>343.0</v>
       </c>
       <c r="Q144" t="n">
         <v>0.0</v>
@@ -10390,7 +10390,7 @@
         <v>1012.0</v>
       </c>
       <c r="J145" t="n">
-        <v>474.0</v>
+        <v>501.0</v>
       </c>
       <c r="K145" t="n">
         <v>1.0</v>
@@ -10402,16 +10402,16 @@
         <v>0.0</v>
       </c>
       <c r="N145" t="n">
-        <v>474.0</v>
+        <v>501.0</v>
       </c>
       <c r="O145" t="n">
-        <v>195.0</v>
+        <v>202.0</v>
       </c>
       <c r="P145" t="n">
-        <v>264.0</v>
+        <v>282.0</v>
       </c>
       <c r="Q145" t="n">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R145" t="n">
         <v>10.0</v>
@@ -10674,7 +10674,7 @@
         <v>1218.0</v>
       </c>
       <c r="J149" t="n">
-        <v>322.0</v>
+        <v>337.0</v>
       </c>
       <c r="K149" t="n">
         <v>1.0</v>
@@ -10686,13 +10686,13 @@
         <v>0.0</v>
       </c>
       <c r="N149" t="n">
-        <v>322.0</v>
+        <v>337.0</v>
       </c>
       <c r="O149" t="n">
-        <v>176.0</v>
+        <v>186.0</v>
       </c>
       <c r="P149" t="n">
-        <v>144.0</v>
+        <v>149.0</v>
       </c>
       <c r="Q149" t="n">
         <v>2.0</v>
@@ -10887,7 +10887,7 @@
         <v>942.0</v>
       </c>
       <c r="J152" t="n">
-        <v>443.0</v>
+        <v>452.0</v>
       </c>
       <c r="K152" t="n">
         <v>1.0</v>
@@ -10899,13 +10899,13 @@
         <v>1.0</v>
       </c>
       <c r="N152" t="n">
-        <v>442.0</v>
+        <v>451.0</v>
       </c>
       <c r="O152" t="n">
-        <v>212.0</v>
+        <v>219.0</v>
       </c>
       <c r="P152" t="n">
-        <v>231.0</v>
+        <v>233.0</v>
       </c>
       <c r="Q152" t="n">
         <v>0.0</v>
@@ -10958,7 +10958,7 @@
         <v>1018.0</v>
       </c>
       <c r="J153" t="n">
-        <v>587.0</v>
+        <v>590.0</v>
       </c>
       <c r="K153" t="n">
         <v>1.0</v>
@@ -10970,13 +10970,13 @@
         <v>0.0</v>
       </c>
       <c r="N153" t="n">
-        <v>587.0</v>
+        <v>590.0</v>
       </c>
       <c r="O153" t="n">
-        <v>288.0</v>
+        <v>289.0</v>
       </c>
       <c r="P153" t="n">
-        <v>299.0</v>
+        <v>301.0</v>
       </c>
       <c r="Q153" t="n">
         <v>0.0</v>
@@ -11029,7 +11029,7 @@
         <v>999.0</v>
       </c>
       <c r="J154" t="n">
-        <v>513.0</v>
+        <v>525.0</v>
       </c>
       <c r="K154" t="n">
         <v>1.0</v>
@@ -11041,16 +11041,16 @@
         <v>0.0</v>
       </c>
       <c r="N154" t="n">
-        <v>513.0</v>
+        <v>525.0</v>
       </c>
       <c r="O154" t="n">
         <v>29.0</v>
       </c>
       <c r="P154" t="n">
-        <v>291.0</v>
+        <v>295.0</v>
       </c>
       <c r="Q154" t="n">
-        <v>193.0</v>
+        <v>201.0</v>
       </c>
       <c r="R154" t="n">
         <v>0.0</v>
@@ -11124,10 +11124,10 @@
         <v>0.0</v>
       </c>
       <c r="R155" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="S155" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T155" t="n">
         <v>0.0</v>
@@ -11139,7 +11139,7 @@
         <v>0.0</v>
       </c>
       <c r="W155" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="156">
@@ -11171,7 +11171,7 @@
         <v>1119.0</v>
       </c>
       <c r="J156" t="n">
-        <v>528.0</v>
+        <v>542.0</v>
       </c>
       <c r="K156" t="n">
         <v>1.0</v>
@@ -11183,13 +11183,13 @@
         <v>0.0</v>
       </c>
       <c r="N156" t="n">
-        <v>528.0</v>
+        <v>542.0</v>
       </c>
       <c r="O156" t="n">
-        <v>172.0</v>
+        <v>178.0</v>
       </c>
       <c r="P156" t="n">
-        <v>355.0</v>
+        <v>363.0</v>
       </c>
       <c r="Q156" t="n">
         <v>1.0</v>
@@ -11242,7 +11242,7 @@
         <v>1501.0</v>
       </c>
       <c r="J157" t="n">
-        <v>487.0</v>
+        <v>490.0</v>
       </c>
       <c r="K157" t="n">
         <v>1.0</v>
@@ -11254,13 +11254,13 @@
         <v>4.0</v>
       </c>
       <c r="N157" t="n">
-        <v>483.0</v>
+        <v>486.0</v>
       </c>
       <c r="O157" t="n">
         <v>141.0</v>
       </c>
       <c r="P157" t="n">
-        <v>346.0</v>
+        <v>349.0</v>
       </c>
       <c r="Q157" t="n">
         <v>0.0</v>
@@ -11313,7 +11313,7 @@
         <v>1353.0</v>
       </c>
       <c r="J158" t="n">
-        <v>605.0</v>
+        <v>615.0</v>
       </c>
       <c r="K158" t="n">
         <v>1.0</v>
@@ -11325,19 +11325,19 @@
         <v>0.0</v>
       </c>
       <c r="N158" t="n">
-        <v>605.0</v>
+        <v>615.0</v>
       </c>
       <c r="O158" t="n">
-        <v>275.0</v>
+        <v>283.0</v>
       </c>
       <c r="P158" t="n">
-        <v>330.0</v>
+        <v>332.0</v>
       </c>
       <c r="Q158" t="n">
         <v>0.0</v>
       </c>
       <c r="R158" t="n">
-        <v>32.0</v>
+        <v>36.0</v>
       </c>
       <c r="S158" t="n">
         <v>0.0</v>
@@ -11352,7 +11352,7 @@
         <v>0.0</v>
       </c>
       <c r="W158" t="n">
-        <v>32.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="159">
@@ -11384,7 +11384,7 @@
         <v>1153.0</v>
       </c>
       <c r="J159" t="n">
-        <v>615.0</v>
+        <v>631.0</v>
       </c>
       <c r="K159" t="n">
         <v>1.0</v>
@@ -11396,13 +11396,13 @@
         <v>1.0</v>
       </c>
       <c r="N159" t="n">
-        <v>614.0</v>
+        <v>630.0</v>
       </c>
       <c r="O159" t="n">
-        <v>346.0</v>
+        <v>354.0</v>
       </c>
       <c r="P159" t="n">
-        <v>269.0</v>
+        <v>277.0</v>
       </c>
       <c r="Q159" t="n">
         <v>0.0</v>
@@ -11668,7 +11668,7 @@
         <v>1298.0</v>
       </c>
       <c r="J163" t="n">
-        <v>656.0</v>
+        <v>657.0</v>
       </c>
       <c r="K163" t="n">
         <v>1.0</v>
@@ -11680,13 +11680,13 @@
         <v>0.0</v>
       </c>
       <c r="N163" t="n">
-        <v>656.0</v>
+        <v>657.0</v>
       </c>
       <c r="O163" t="n">
         <v>8.0</v>
       </c>
       <c r="P163" t="n">
-        <v>298.0</v>
+        <v>299.0</v>
       </c>
       <c r="Q163" t="n">
         <v>350.0</v>
@@ -11810,7 +11810,7 @@
         <v>421.0</v>
       </c>
       <c r="J165" t="n">
-        <v>331.0</v>
+        <v>332.0</v>
       </c>
       <c r="K165" t="n">
         <v>1.0</v>
@@ -11822,7 +11822,7 @@
         <v>0.0</v>
       </c>
       <c r="N165" t="n">
-        <v>331.0</v>
+        <v>332.0</v>
       </c>
       <c r="O165" t="n">
         <v>181.0</v>
@@ -11831,7 +11831,7 @@
         <v>143.0</v>
       </c>
       <c r="Q165" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="R165" t="n">
         <v>0.0</v>
@@ -11843,13 +11843,13 @@
         <v>0.0</v>
       </c>
       <c r="U165" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="V165" t="n">
         <v>0.0</v>
       </c>
       <c r="W165" t="n">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="166">
@@ -11881,7 +11881,7 @@
         <v>932.0</v>
       </c>
       <c r="J166" t="n">
-        <v>501.0</v>
+        <v>505.0</v>
       </c>
       <c r="K166" t="n">
         <v>1.0</v>
@@ -11893,10 +11893,10 @@
         <v>0.0</v>
       </c>
       <c r="N166" t="n">
-        <v>501.0</v>
+        <v>505.0</v>
       </c>
       <c r="O166" t="n">
-        <v>261.0</v>
+        <v>265.0</v>
       </c>
       <c r="P166" t="n">
         <v>240.0</v>
@@ -11952,7 +11952,7 @@
         <v>667.0</v>
       </c>
       <c r="J167" t="n">
-        <v>504.0</v>
+        <v>530.0</v>
       </c>
       <c r="K167" t="n">
         <v>1.0</v>
@@ -11964,13 +11964,13 @@
         <v>0.0</v>
       </c>
       <c r="N167" t="n">
-        <v>504.0</v>
+        <v>530.0</v>
       </c>
       <c r="O167" t="n">
-        <v>242.0</v>
+        <v>257.0</v>
       </c>
       <c r="P167" t="n">
-        <v>262.0</v>
+        <v>273.0</v>
       </c>
       <c r="Q167" t="n">
         <v>0.0</v>
@@ -12023,7 +12023,7 @@
         <v>948.0</v>
       </c>
       <c r="J168" t="n">
-        <v>445.0</v>
+        <v>454.0</v>
       </c>
       <c r="K168" t="n">
         <v>1.0</v>
@@ -12035,13 +12035,13 @@
         <v>0.0</v>
       </c>
       <c r="N168" t="n">
-        <v>445.0</v>
+        <v>454.0</v>
       </c>
       <c r="O168" t="n">
-        <v>123.0</v>
+        <v>127.0</v>
       </c>
       <c r="P168" t="n">
-        <v>234.0</v>
+        <v>239.0</v>
       </c>
       <c r="Q168" t="n">
         <v>88.0</v>
@@ -12094,7 +12094,7 @@
         <v>503.0</v>
       </c>
       <c r="J169" t="n">
-        <v>319.0</v>
+        <v>330.0</v>
       </c>
       <c r="K169" t="n">
         <v>1.0</v>
@@ -12106,13 +12106,13 @@
         <v>0.0</v>
       </c>
       <c r="N169" t="n">
-        <v>319.0</v>
+        <v>330.0</v>
       </c>
       <c r="O169" t="n">
-        <v>114.0</v>
+        <v>123.0</v>
       </c>
       <c r="P169" t="n">
-        <v>197.0</v>
+        <v>199.0</v>
       </c>
       <c r="Q169" t="n">
         <v>8.0</v>
@@ -12307,7 +12307,7 @@
         <v>1079.0</v>
       </c>
       <c r="J172" t="n">
-        <v>247.0</v>
+        <v>275.0</v>
       </c>
       <c r="K172" t="n">
         <v>1.0</v>
@@ -12319,13 +12319,13 @@
         <v>0.0</v>
       </c>
       <c r="N172" t="n">
-        <v>247.0</v>
+        <v>275.0</v>
       </c>
       <c r="O172" t="n">
-        <v>70.0</v>
+        <v>93.0</v>
       </c>
       <c r="P172" t="n">
-        <v>177.0</v>
+        <v>182.0</v>
       </c>
       <c r="Q172" t="n">
         <v>0.0</v>
@@ -12449,7 +12449,7 @@
         <v>1280.0</v>
       </c>
       <c r="J174" t="n">
-        <v>829.0</v>
+        <v>870.0</v>
       </c>
       <c r="K174" t="n">
         <v>1.0</v>
@@ -12461,13 +12461,13 @@
         <v>0.0</v>
       </c>
       <c r="N174" t="n">
-        <v>829.0</v>
+        <v>870.0</v>
       </c>
       <c r="O174" t="n">
-        <v>410.0</v>
+        <v>431.0</v>
       </c>
       <c r="P174" t="n">
-        <v>419.0</v>
+        <v>439.0</v>
       </c>
       <c r="Q174" t="n">
         <v>0.0</v>
@@ -12591,7 +12591,7 @@
         <v>1045.0</v>
       </c>
       <c r="J176" t="n">
-        <v>357.0</v>
+        <v>377.0</v>
       </c>
       <c r="K176" t="n">
         <v>1.0</v>
@@ -12603,13 +12603,13 @@
         <v>0.0</v>
       </c>
       <c r="N176" t="n">
-        <v>357.0</v>
+        <v>377.0</v>
       </c>
       <c r="O176" t="n">
-        <v>143.0</v>
+        <v>150.0</v>
       </c>
       <c r="P176" t="n">
-        <v>214.0</v>
+        <v>227.0</v>
       </c>
       <c r="Q176" t="n">
         <v>0.0</v>
@@ -12624,13 +12624,13 @@
         <v>0.0</v>
       </c>
       <c r="U176" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V176" t="n">
         <v>0.0</v>
       </c>
       <c r="W176" t="n">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="177">
@@ -12662,7 +12662,7 @@
         <v>1075.0</v>
       </c>
       <c r="J177" t="n">
-        <v>298.0</v>
+        <v>303.0</v>
       </c>
       <c r="K177" t="n">
         <v>1.0</v>
@@ -12674,34 +12674,34 @@
         <v>0.0</v>
       </c>
       <c r="N177" t="n">
-        <v>298.0</v>
+        <v>303.0</v>
       </c>
       <c r="O177" t="n">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="P177" t="n">
-        <v>171.0</v>
+        <v>175.0</v>
       </c>
       <c r="Q177" t="n">
         <v>0.0</v>
       </c>
       <c r="R177" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="S177" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="T177" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U177" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="V177" t="n">
         <v>0.0</v>
       </c>
       <c r="W177" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="178">
@@ -12733,7 +12733,7 @@
         <v>1008.0</v>
       </c>
       <c r="J178" t="n">
-        <v>297.0</v>
+        <v>310.0</v>
       </c>
       <c r="K178" t="n">
         <v>1.0</v>
@@ -12745,13 +12745,13 @@
         <v>0.0</v>
       </c>
       <c r="N178" t="n">
-        <v>297.0</v>
+        <v>310.0</v>
       </c>
       <c r="O178" t="n">
-        <v>136.0</v>
+        <v>144.0</v>
       </c>
       <c r="P178" t="n">
-        <v>160.0</v>
+        <v>165.0</v>
       </c>
       <c r="Q178" t="n">
         <v>1.0</v>
@@ -12766,13 +12766,13 @@
         <v>0.0</v>
       </c>
       <c r="U178" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="V178" t="n">
         <v>0.0</v>
       </c>
       <c r="W178" t="n">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="179">
@@ -12804,7 +12804,7 @@
         <v>1061.0</v>
       </c>
       <c r="J179" t="n">
-        <v>466.0</v>
+        <v>483.0</v>
       </c>
       <c r="K179" t="n">
         <v>1.0</v>
@@ -12816,16 +12816,16 @@
         <v>0.0</v>
       </c>
       <c r="N179" t="n">
-        <v>466.0</v>
+        <v>483.0</v>
       </c>
       <c r="O179" t="n">
-        <v>273.0</v>
+        <v>284.0</v>
       </c>
       <c r="P179" t="n">
-        <v>193.0</v>
+        <v>198.0</v>
       </c>
       <c r="Q179" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R179" t="n">
         <v>9.0</v>
@@ -12875,7 +12875,7 @@
         <v>781.0</v>
       </c>
       <c r="J180" t="n">
-        <v>315.0</v>
+        <v>316.0</v>
       </c>
       <c r="K180" t="n">
         <v>1.0</v>
@@ -12887,10 +12887,10 @@
         <v>0.0</v>
       </c>
       <c r="N180" t="n">
-        <v>315.0</v>
+        <v>316.0</v>
       </c>
       <c r="O180" t="n">
-        <v>163.0</v>
+        <v>164.0</v>
       </c>
       <c r="P180" t="n">
         <v>152.0</v>
@@ -12899,10 +12899,10 @@
         <v>0.0</v>
       </c>
       <c r="R180" t="n">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="S180" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="T180" t="n">
         <v>0.0</v>
@@ -12914,7 +12914,7 @@
         <v>0.0</v>
       </c>
       <c r="W180" t="n">
-        <v>11.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="181">
@@ -13017,7 +13017,7 @@
         <v>753.0</v>
       </c>
       <c r="J182" t="n">
-        <v>502.0</v>
+        <v>521.0</v>
       </c>
       <c r="K182" t="n">
         <v>1.0</v>
@@ -13029,13 +13029,13 @@
         <v>0.0</v>
       </c>
       <c r="N182" t="n">
-        <v>502.0</v>
+        <v>521.0</v>
       </c>
       <c r="O182" t="n">
-        <v>224.0</v>
+        <v>231.0</v>
       </c>
       <c r="P182" t="n">
-        <v>277.0</v>
+        <v>289.0</v>
       </c>
       <c r="Q182" t="n">
         <v>1.0</v>
@@ -13301,7 +13301,7 @@
         <v>1067.0</v>
       </c>
       <c r="J186" t="n">
-        <v>529.0</v>
+        <v>539.0</v>
       </c>
       <c r="K186" t="n">
         <v>1.0</v>
@@ -13313,16 +13313,16 @@
         <v>0.0</v>
       </c>
       <c r="N186" t="n">
-        <v>529.0</v>
+        <v>539.0</v>
       </c>
       <c r="O186" t="n">
         <v>118.0</v>
       </c>
       <c r="P186" t="n">
-        <v>259.0</v>
+        <v>262.0</v>
       </c>
       <c r="Q186" t="n">
-        <v>152.0</v>
+        <v>159.0</v>
       </c>
       <c r="R186" t="n">
         <v>1.0</v>
@@ -13372,7 +13372,7 @@
         <v>990.0</v>
       </c>
       <c r="J187" t="n">
-        <v>643.0</v>
+        <v>655.0</v>
       </c>
       <c r="K187" t="n">
         <v>1.0</v>
@@ -13384,13 +13384,13 @@
         <v>0.0</v>
       </c>
       <c r="N187" t="n">
-        <v>643.0</v>
+        <v>655.0</v>
       </c>
       <c r="O187" t="n">
-        <v>390.0</v>
+        <v>399.0</v>
       </c>
       <c r="P187" t="n">
-        <v>253.0</v>
+        <v>256.0</v>
       </c>
       <c r="Q187" t="n">
         <v>0.0</v>
@@ -13467,10 +13467,10 @@
         <v>58.0</v>
       </c>
       <c r="R188" t="n">
-        <v>59.0</v>
+        <v>65.0</v>
       </c>
       <c r="S188" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="T188" t="n">
         <v>0.0</v>
@@ -13482,7 +13482,7 @@
         <v>0.0</v>
       </c>
       <c r="W188" t="n">
-        <v>67.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="189">
@@ -13514,7 +13514,7 @@
         <v>1282.0</v>
       </c>
       <c r="J189" t="n">
-        <v>476.0</v>
+        <v>480.0</v>
       </c>
       <c r="K189" t="n">
         <v>1.0</v>
@@ -13526,13 +13526,13 @@
         <v>0.0</v>
       </c>
       <c r="N189" t="n">
-        <v>476.0</v>
+        <v>480.0</v>
       </c>
       <c r="O189" t="n">
-        <v>90.0</v>
+        <v>92.0</v>
       </c>
       <c r="P189" t="n">
-        <v>116.0</v>
+        <v>118.0</v>
       </c>
       <c r="Q189" t="n">
         <v>270.0</v>
@@ -13585,7 +13585,7 @@
         <v>1393.0</v>
       </c>
       <c r="J190" t="n">
-        <v>627.0</v>
+        <v>639.0</v>
       </c>
       <c r="K190" t="n">
         <v>1.0</v>
@@ -13597,13 +13597,13 @@
         <v>0.0</v>
       </c>
       <c r="N190" t="n">
-        <v>627.0</v>
+        <v>639.0</v>
       </c>
       <c r="O190" t="n">
-        <v>308.0</v>
+        <v>315.0</v>
       </c>
       <c r="P190" t="n">
-        <v>298.0</v>
+        <v>303.0</v>
       </c>
       <c r="Q190" t="n">
         <v>21.0</v>
@@ -13727,7 +13727,7 @@
         <v>508.0</v>
       </c>
       <c r="J192" t="n">
-        <v>319.0</v>
+        <v>320.0</v>
       </c>
       <c r="K192" t="n">
         <v>1.0</v>
@@ -13739,13 +13739,13 @@
         <v>0.0</v>
       </c>
       <c r="N192" t="n">
-        <v>319.0</v>
+        <v>320.0</v>
       </c>
       <c r="O192" t="n">
         <v>174.0</v>
       </c>
       <c r="P192" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="Q192" t="n">
         <v>2.0</v>
@@ -13940,7 +13940,7 @@
         <v>556.0</v>
       </c>
       <c r="J195" t="n">
-        <v>273.0</v>
+        <v>288.0</v>
       </c>
       <c r="K195" t="n">
         <v>1.0</v>
@@ -13952,16 +13952,16 @@
         <v>0.0</v>
       </c>
       <c r="N195" t="n">
-        <v>273.0</v>
+        <v>288.0</v>
       </c>
       <c r="O195" t="n">
         <v>71.0</v>
       </c>
       <c r="P195" t="n">
-        <v>124.0</v>
+        <v>127.0</v>
       </c>
       <c r="Q195" t="n">
-        <v>78.0</v>
+        <v>90.0</v>
       </c>
       <c r="R195" t="n">
         <v>0.0</v>
@@ -14011,7 +14011,7 @@
         <v>1391.0</v>
       </c>
       <c r="J196" t="n">
-        <v>966.0</v>
+        <v>1011.0</v>
       </c>
       <c r="K196" t="n">
         <v>1.0</v>
@@ -14023,16 +14023,16 @@
         <v>0.0</v>
       </c>
       <c r="N196" t="n">
-        <v>966.0</v>
+        <v>1011.0</v>
       </c>
       <c r="O196" t="n">
-        <v>369.0</v>
+        <v>387.0</v>
       </c>
       <c r="P196" t="n">
-        <v>415.0</v>
+        <v>438.0</v>
       </c>
       <c r="Q196" t="n">
-        <v>182.0</v>
+        <v>186.0</v>
       </c>
       <c r="R196" t="n">
         <v>0.0</v>
@@ -14082,7 +14082,7 @@
         <v>1163.0</v>
       </c>
       <c r="J197" t="n">
-        <v>991.0</v>
+        <v>993.0</v>
       </c>
       <c r="K197" t="n">
         <v>1.0</v>
@@ -14094,13 +14094,13 @@
         <v>0.0</v>
       </c>
       <c r="N197" t="n">
-        <v>991.0</v>
+        <v>993.0</v>
       </c>
       <c r="O197" t="n">
         <v>548.0</v>
       </c>
       <c r="P197" t="n">
-        <v>330.0</v>
+        <v>332.0</v>
       </c>
       <c r="Q197" t="n">
         <v>113.0</v>
@@ -14224,7 +14224,7 @@
         <v>1015.0</v>
       </c>
       <c r="J199" t="n">
-        <v>517.0</v>
+        <v>550.0</v>
       </c>
       <c r="K199" t="n">
         <v>1.0</v>
@@ -14236,13 +14236,13 @@
         <v>0.0</v>
       </c>
       <c r="N199" t="n">
-        <v>517.0</v>
+        <v>550.0</v>
       </c>
       <c r="O199" t="n">
-        <v>188.0</v>
+        <v>198.0</v>
       </c>
       <c r="P199" t="n">
-        <v>329.0</v>
+        <v>352.0</v>
       </c>
       <c r="Q199" t="n">
         <v>0.0</v>
@@ -14295,7 +14295,7 @@
         <v>704.0</v>
       </c>
       <c r="J200" t="n">
-        <v>396.0</v>
+        <v>407.0</v>
       </c>
       <c r="K200" t="n">
         <v>1.0</v>
@@ -14307,13 +14307,13 @@
         <v>0.0</v>
       </c>
       <c r="N200" t="n">
-        <v>396.0</v>
+        <v>407.0</v>
       </c>
       <c r="O200" t="n">
-        <v>233.0</v>
+        <v>241.0</v>
       </c>
       <c r="P200" t="n">
-        <v>160.0</v>
+        <v>163.0</v>
       </c>
       <c r="Q200" t="n">
         <v>3.0</v>
@@ -14366,7 +14366,7 @@
         <v>1283.0</v>
       </c>
       <c r="J201" t="n">
-        <v>636.0</v>
+        <v>637.0</v>
       </c>
       <c r="K201" t="n">
         <v>1.0</v>
@@ -14378,10 +14378,10 @@
         <v>0.0</v>
       </c>
       <c r="N201" t="n">
-        <v>636.0</v>
+        <v>637.0</v>
       </c>
       <c r="O201" t="n">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="P201" t="n">
         <v>303.0</v>
@@ -14390,13 +14390,13 @@
         <v>4.0</v>
       </c>
       <c r="R201" t="n">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="S201" t="n">
         <v>16.0</v>
       </c>
       <c r="T201" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="U201" t="n">
         <v>8.0</v>
@@ -14405,7 +14405,7 @@
         <v>1.0</v>
       </c>
       <c r="W201" t="n">
-        <v>48.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="202">
@@ -14437,7 +14437,7 @@
         <v>1172.0</v>
       </c>
       <c r="J202" t="n">
-        <v>284.0</v>
+        <v>292.0</v>
       </c>
       <c r="K202" t="n">
         <v>1.0</v>
@@ -14449,13 +14449,13 @@
         <v>0.0</v>
       </c>
       <c r="N202" t="n">
-        <v>284.0</v>
+        <v>292.0</v>
       </c>
       <c r="O202" t="n">
-        <v>153.0</v>
+        <v>156.0</v>
       </c>
       <c r="P202" t="n">
-        <v>131.0</v>
+        <v>136.0</v>
       </c>
       <c r="Q202" t="n">
         <v>0.0</v>
@@ -14508,7 +14508,7 @@
         <v>1257.0</v>
       </c>
       <c r="J203" t="n">
-        <v>474.0</v>
+        <v>510.0</v>
       </c>
       <c r="K203" t="n">
         <v>1.0</v>
@@ -14520,13 +14520,13 @@
         <v>0.0</v>
       </c>
       <c r="N203" t="n">
-        <v>474.0</v>
+        <v>510.0</v>
       </c>
       <c r="O203" t="n">
-        <v>260.0</v>
+        <v>280.0</v>
       </c>
       <c r="P203" t="n">
-        <v>214.0</v>
+        <v>230.0</v>
       </c>
       <c r="Q203" t="n">
         <v>0.0</v>
@@ -14650,7 +14650,7 @@
         <v>897.0</v>
       </c>
       <c r="J205" t="n">
-        <v>243.0</v>
+        <v>248.0</v>
       </c>
       <c r="K205" t="n">
         <v>1.0</v>
@@ -14662,13 +14662,13 @@
         <v>0.0</v>
       </c>
       <c r="N205" t="n">
-        <v>243.0</v>
+        <v>248.0</v>
       </c>
       <c r="O205" t="n">
-        <v>119.0</v>
+        <v>122.0</v>
       </c>
       <c r="P205" t="n">
-        <v>114.0</v>
+        <v>116.0</v>
       </c>
       <c r="Q205" t="n">
         <v>10.0</v>
@@ -14792,7 +14792,7 @@
         <v>943.0</v>
       </c>
       <c r="J207" t="n">
-        <v>367.0</v>
+        <v>372.0</v>
       </c>
       <c r="K207" t="n">
         <v>1.0</v>
@@ -14804,13 +14804,13 @@
         <v>0.0</v>
       </c>
       <c r="N207" t="n">
-        <v>367.0</v>
+        <v>372.0</v>
       </c>
       <c r="O207" t="n">
-        <v>208.0</v>
+        <v>211.0</v>
       </c>
       <c r="P207" t="n">
-        <v>155.0</v>
+        <v>157.0</v>
       </c>
       <c r="Q207" t="n">
         <v>4.0</v>
@@ -14934,7 +14934,7 @@
         <v>951.0</v>
       </c>
       <c r="J209" t="n">
-        <v>703.0</v>
+        <v>704.0</v>
       </c>
       <c r="K209" t="n">
         <v>1.0</v>
@@ -14946,13 +14946,13 @@
         <v>0.0</v>
       </c>
       <c r="N209" t="n">
-        <v>703.0</v>
+        <v>704.0</v>
       </c>
       <c r="O209" t="n">
         <v>352.0</v>
       </c>
       <c r="P209" t="n">
-        <v>351.0</v>
+        <v>352.0</v>
       </c>
       <c r="Q209" t="n">
         <v>0.0</v>
@@ -15005,7 +15005,7 @@
         <v>792.0</v>
       </c>
       <c r="J210" t="n">
-        <v>546.0</v>
+        <v>568.0</v>
       </c>
       <c r="K210" t="n">
         <v>1.0</v>
@@ -15017,13 +15017,13 @@
         <v>0.0</v>
       </c>
       <c r="N210" t="n">
-        <v>546.0</v>
+        <v>568.0</v>
       </c>
       <c r="O210" t="n">
-        <v>254.0</v>
+        <v>269.0</v>
       </c>
       <c r="P210" t="n">
-        <v>292.0</v>
+        <v>299.0</v>
       </c>
       <c r="Q210" t="n">
         <v>0.0</v>
@@ -15076,7 +15076,7 @@
         <v>1074.0</v>
       </c>
       <c r="J211" t="n">
-        <v>765.0</v>
+        <v>768.0</v>
       </c>
       <c r="K211" t="n">
         <v>1.0</v>
@@ -15088,19 +15088,19 @@
         <v>0.0</v>
       </c>
       <c r="N211" t="n">
-        <v>765.0</v>
+        <v>768.0</v>
       </c>
       <c r="O211" t="n">
-        <v>393.0</v>
+        <v>395.0</v>
       </c>
       <c r="P211" t="n">
-        <v>372.0</v>
+        <v>373.0</v>
       </c>
       <c r="Q211" t="n">
         <v>0.0</v>
       </c>
       <c r="R211" t="n">
-        <v>52.0</v>
+        <v>65.0</v>
       </c>
       <c r="S211" t="n">
         <v>0.0</v>
@@ -15115,7 +15115,7 @@
         <v>0.0</v>
       </c>
       <c r="W211" t="n">
-        <v>52.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="212">
@@ -15147,7 +15147,7 @@
         <v>1055.0</v>
       </c>
       <c r="J212" t="n">
-        <v>584.0</v>
+        <v>615.0</v>
       </c>
       <c r="K212" t="n">
         <v>1.0</v>
@@ -15159,16 +15159,16 @@
         <v>1.0</v>
       </c>
       <c r="N212" t="n">
-        <v>583.0</v>
+        <v>614.0</v>
       </c>
       <c r="O212" t="n">
-        <v>134.0</v>
+        <v>143.0</v>
       </c>
       <c r="P212" t="n">
-        <v>265.0</v>
+        <v>282.0</v>
       </c>
       <c r="Q212" t="n">
-        <v>185.0</v>
+        <v>190.0</v>
       </c>
       <c r="R212" t="n">
         <v>4.0</v>
@@ -15218,7 +15218,7 @@
         <v>1034.0</v>
       </c>
       <c r="J213" t="n">
-        <v>516.0</v>
+        <v>525.0</v>
       </c>
       <c r="K213" t="n">
         <v>1.0</v>
@@ -15230,13 +15230,13 @@
         <v>0.0</v>
       </c>
       <c r="N213" t="n">
-        <v>516.0</v>
+        <v>525.0</v>
       </c>
       <c r="O213" t="n">
-        <v>260.0</v>
+        <v>264.0</v>
       </c>
       <c r="P213" t="n">
-        <v>256.0</v>
+        <v>261.0</v>
       </c>
       <c r="Q213" t="n">
         <v>0.0</v>
@@ -15289,7 +15289,7 @@
         <v>1038.0</v>
       </c>
       <c r="J214" t="n">
-        <v>365.0</v>
+        <v>385.0</v>
       </c>
       <c r="K214" t="n">
         <v>1.0</v>
@@ -15301,13 +15301,13 @@
         <v>0.0</v>
       </c>
       <c r="N214" t="n">
-        <v>365.0</v>
+        <v>385.0</v>
       </c>
       <c r="O214" t="n">
-        <v>187.0</v>
+        <v>194.0</v>
       </c>
       <c r="P214" t="n">
-        <v>178.0</v>
+        <v>191.0</v>
       </c>
       <c r="Q214" t="n">
         <v>0.0</v>
@@ -15360,7 +15360,7 @@
         <v>1067.0</v>
       </c>
       <c r="J215" t="n">
-        <v>546.0</v>
+        <v>555.0</v>
       </c>
       <c r="K215" t="n">
         <v>1.0</v>
@@ -15372,13 +15372,13 @@
         <v>0.0</v>
       </c>
       <c r="N215" t="n">
-        <v>546.0</v>
+        <v>555.0</v>
       </c>
       <c r="O215" t="n">
-        <v>216.0</v>
+        <v>221.0</v>
       </c>
       <c r="P215" t="n">
-        <v>330.0</v>
+        <v>334.0</v>
       </c>
       <c r="Q215" t="n">
         <v>0.0</v>
@@ -15387,7 +15387,7 @@
         <v>8.0</v>
       </c>
       <c r="S215" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="T215" t="n">
         <v>3.0</v>
@@ -15399,7 +15399,7 @@
         <v>0.0</v>
       </c>
       <c r="W215" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="216">
@@ -15431,7 +15431,7 @@
         <v>576.0</v>
       </c>
       <c r="J216" t="n">
-        <v>239.0</v>
+        <v>242.0</v>
       </c>
       <c r="K216" t="n">
         <v>1.0</v>
@@ -15443,16 +15443,16 @@
         <v>0.0</v>
       </c>
       <c r="N216" t="n">
-        <v>239.0</v>
+        <v>242.0</v>
       </c>
       <c r="O216" t="n">
         <v>132.0</v>
       </c>
       <c r="P216" t="n">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="Q216" t="n">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="R216" t="n">
         <v>0.0</v>
@@ -15502,7 +15502,7 @@
         <v>1136.0</v>
       </c>
       <c r="J217" t="n">
-        <v>545.0</v>
+        <v>548.0</v>
       </c>
       <c r="K217" t="n">
         <v>1.0</v>
@@ -15514,13 +15514,13 @@
         <v>0.0</v>
       </c>
       <c r="N217" t="n">
-        <v>545.0</v>
+        <v>548.0</v>
       </c>
       <c r="O217" t="n">
-        <v>233.0</v>
+        <v>234.0</v>
       </c>
       <c r="P217" t="n">
-        <v>312.0</v>
+        <v>314.0</v>
       </c>
       <c r="Q217" t="n">
         <v>0.0</v>
@@ -15715,7 +15715,7 @@
         <v>867.0</v>
       </c>
       <c r="J220" t="n">
-        <v>529.0</v>
+        <v>530.0</v>
       </c>
       <c r="K220" t="n">
         <v>1.0</v>
@@ -15727,13 +15727,13 @@
         <v>0.0</v>
       </c>
       <c r="N220" t="n">
-        <v>529.0</v>
+        <v>530.0</v>
       </c>
       <c r="O220" t="n">
         <v>90.0</v>
       </c>
       <c r="P220" t="n">
-        <v>247.0</v>
+        <v>248.0</v>
       </c>
       <c r="Q220" t="n">
         <v>192.0</v>
@@ -15786,7 +15786,7 @@
         <v>848.0</v>
       </c>
       <c r="J221" t="n">
-        <v>503.0</v>
+        <v>507.0</v>
       </c>
       <c r="K221" t="n">
         <v>1.0</v>
@@ -15798,16 +15798,16 @@
         <v>1.0</v>
       </c>
       <c r="N221" t="n">
-        <v>502.0</v>
+        <v>506.0</v>
       </c>
       <c r="O221" t="n">
         <v>115.0</v>
       </c>
       <c r="P221" t="n">
-        <v>228.0</v>
+        <v>230.0</v>
       </c>
       <c r="Q221" t="n">
-        <v>160.0</v>
+        <v>162.0</v>
       </c>
       <c r="R221" t="n">
         <v>0.0</v>
@@ -15857,7 +15857,7 @@
         <v>1043.0</v>
       </c>
       <c r="J222" t="n">
-        <v>531.0</v>
+        <v>544.0</v>
       </c>
       <c r="K222" t="n">
         <v>1.0</v>
@@ -15869,16 +15869,16 @@
         <v>0.0</v>
       </c>
       <c r="N222" t="n">
-        <v>531.0</v>
+        <v>544.0</v>
       </c>
       <c r="O222" t="n">
         <v>126.0</v>
       </c>
       <c r="P222" t="n">
-        <v>226.0</v>
+        <v>228.0</v>
       </c>
       <c r="Q222" t="n">
-        <v>179.0</v>
+        <v>190.0</v>
       </c>
       <c r="R222" t="n">
         <v>0.0</v>
@@ -15928,7 +15928,7 @@
         <v>1272.0</v>
       </c>
       <c r="J223" t="n">
-        <v>647.0</v>
+        <v>657.0</v>
       </c>
       <c r="K223" t="n">
         <v>1.0</v>
@@ -15940,16 +15940,16 @@
         <v>0.0</v>
       </c>
       <c r="N223" t="n">
-        <v>647.0</v>
+        <v>657.0</v>
       </c>
       <c r="O223" t="n">
         <v>66.0</v>
       </c>
       <c r="P223" t="n">
-        <v>229.0</v>
+        <v>233.0</v>
       </c>
       <c r="Q223" t="n">
-        <v>352.0</v>
+        <v>358.0</v>
       </c>
       <c r="R223" t="n">
         <v>0.0</v>
@@ -16070,7 +16070,7 @@
         <v>1423.0</v>
       </c>
       <c r="J225" t="n">
-        <v>1068.0</v>
+        <v>1077.0</v>
       </c>
       <c r="K225" t="n">
         <v>1.0</v>
@@ -16082,13 +16082,13 @@
         <v>0.0</v>
       </c>
       <c r="N225" t="n">
-        <v>1068.0</v>
+        <v>1077.0</v>
       </c>
       <c r="O225" t="n">
-        <v>618.0</v>
+        <v>621.0</v>
       </c>
       <c r="P225" t="n">
-        <v>450.0</v>
+        <v>456.0</v>
       </c>
       <c r="Q225" t="n">
         <v>0.0</v>
@@ -16141,7 +16141,7 @@
         <v>1256.0</v>
       </c>
       <c r="J226" t="n">
-        <v>509.0</v>
+        <v>514.0</v>
       </c>
       <c r="K226" t="n">
         <v>1.0</v>
@@ -16153,16 +16153,16 @@
         <v>0.0</v>
       </c>
       <c r="N226" t="n">
-        <v>509.0</v>
+        <v>514.0</v>
       </c>
       <c r="O226" t="n">
         <v>45.0</v>
       </c>
       <c r="P226" t="n">
-        <v>250.0</v>
+        <v>253.0</v>
       </c>
       <c r="Q226" t="n">
-        <v>214.0</v>
+        <v>216.0</v>
       </c>
       <c r="R226" t="n">
         <v>14.0</v>
@@ -16212,7 +16212,7 @@
         <v>428.0</v>
       </c>
       <c r="J227" t="n">
-        <v>197.0</v>
+        <v>209.0</v>
       </c>
       <c r="K227" t="n">
         <v>1.0</v>
@@ -16224,13 +16224,13 @@
         <v>0.0</v>
       </c>
       <c r="N227" t="n">
-        <v>197.0</v>
+        <v>209.0</v>
       </c>
       <c r="O227" t="n">
-        <v>114.0</v>
+        <v>120.0</v>
       </c>
       <c r="P227" t="n">
-        <v>83.0</v>
+        <v>89.0</v>
       </c>
       <c r="Q227" t="n">
         <v>0.0</v>
@@ -16354,7 +16354,7 @@
         <v>832.0</v>
       </c>
       <c r="J229" t="n">
-        <v>774.0</v>
+        <v>779.0</v>
       </c>
       <c r="K229" t="n">
         <v>1.0</v>
@@ -16366,16 +16366,16 @@
         <v>0.0</v>
       </c>
       <c r="N229" t="n">
-        <v>774.0</v>
+        <v>779.0</v>
       </c>
       <c r="O229" t="n">
-        <v>421.0</v>
+        <v>440.0</v>
       </c>
       <c r="P229" t="n">
-        <v>335.0</v>
+        <v>336.0</v>
       </c>
       <c r="Q229" t="n">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="R229" t="n">
         <v>0.0</v>
@@ -16425,7 +16425,7 @@
         <v>934.0</v>
       </c>
       <c r="J230" t="n">
-        <v>381.0</v>
+        <v>397.0</v>
       </c>
       <c r="K230" t="n">
         <v>1.0</v>
@@ -16437,16 +16437,16 @@
         <v>0.0</v>
       </c>
       <c r="N230" t="n">
-        <v>381.0</v>
+        <v>397.0</v>
       </c>
       <c r="O230" t="n">
-        <v>65.0</v>
+        <v>69.0</v>
       </c>
       <c r="P230" t="n">
-        <v>174.0</v>
+        <v>181.0</v>
       </c>
       <c r="Q230" t="n">
-        <v>142.0</v>
+        <v>147.0</v>
       </c>
       <c r="R230" t="n">
         <v>0.0</v>
@@ -16496,7 +16496,7 @@
         <v>1070.0</v>
       </c>
       <c r="J231" t="n">
-        <v>557.0</v>
+        <v>577.0</v>
       </c>
       <c r="K231" t="n">
         <v>1.0</v>
@@ -16508,13 +16508,13 @@
         <v>0.0</v>
       </c>
       <c r="N231" t="n">
-        <v>557.0</v>
+        <v>577.0</v>
       </c>
       <c r="O231" t="n">
-        <v>286.0</v>
+        <v>299.0</v>
       </c>
       <c r="P231" t="n">
-        <v>250.0</v>
+        <v>257.0</v>
       </c>
       <c r="Q231" t="n">
         <v>21.0</v>
@@ -16567,7 +16567,7 @@
         <v>1369.0</v>
       </c>
       <c r="J232" t="n">
-        <v>448.0</v>
+        <v>489.0</v>
       </c>
       <c r="K232" t="n">
         <v>1.0</v>
@@ -16579,19 +16579,19 @@
         <v>0.0</v>
       </c>
       <c r="N232" t="n">
-        <v>448.0</v>
+        <v>489.0</v>
       </c>
       <c r="O232" t="n">
         <v>5.0</v>
       </c>
       <c r="P232" t="n">
-        <v>53.0</v>
+        <v>68.0</v>
       </c>
       <c r="Q232" t="n">
-        <v>390.0</v>
+        <v>416.0</v>
       </c>
       <c r="R232" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S232" t="n">
         <v>0.0</v>
@@ -16606,7 +16606,7 @@
         <v>0.0</v>
       </c>
       <c r="W232" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="233">
